--- a/test_data/mycobot_280.xlsx
+++ b/test_data/mycobot_280.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="5" activeTab="5"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="10" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="get_modify_version" sheetId="4" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="get_fresh_mode" sheetId="15" r:id="rId14"/>
     <sheet name="get_angles" sheetId="3" r:id="rId15"/>
     <sheet name="send_angle" sheetId="16" r:id="rId16"/>
+    <sheet name="send_angles" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="125">
   <si>
     <t>ID</t>
   </si>
@@ -306,6 +307,117 @@
   </si>
   <si>
     <t>设置速度超限</t>
+  </si>
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>刷新模式下正确设置多关节角度，速度10</t>
+  </si>
+  <si>
+    <t>send_angles</t>
+  </si>
+  <si>
+    <t>[50,50,50,50,50,50]</t>
+  </si>
+  <si>
+    <t>刷新模式下正确设置多关节角度，速度50</t>
+  </si>
+  <si>
+    <t>[-50,-50,-50,-50,-50,-50]</t>
+  </si>
+  <si>
+    <t>刷新模式下正确设置多关节角度，速度100</t>
+  </si>
+  <si>
+    <t>[45,45,-90,60,60,60]</t>
+  </si>
+  <si>
+    <t>插补模式下正确设置多关节角度，速度10</t>
+  </si>
+  <si>
+    <t>插补模式下正确设置多关节角度，速度50</t>
+  </si>
+  <si>
+    <t>插补模式下正确设置多关节角度，速度100</t>
+  </si>
+  <si>
+    <t>设置多关节，1关节超限（170）</t>
+  </si>
+  <si>
+    <t>[170,0,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，1关节超限（-170）</t>
+  </si>
+  <si>
+    <t>[-170,0,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，2关节超限（170）</t>
+  </si>
+  <si>
+    <t>[0,170,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，2关节超限（-170）</t>
+  </si>
+  <si>
+    <t>[0,-170,0,0,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，3关节超限（170）</t>
+  </si>
+  <si>
+    <t>[0,0,170,0,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，3关节超限（-170）</t>
+  </si>
+  <si>
+    <t>[0,0,-170,0,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，4关节超限（170）</t>
+  </si>
+  <si>
+    <t>[0,0,0,170,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，4关节超限（-170）</t>
+  </si>
+  <si>
+    <t>[0,0,0,-170,0,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，5关节超限（170）</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,170,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，5关节超限（-170）</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,-170,0]</t>
+  </si>
+  <si>
+    <t>设置多关节，6关节超限（-190）</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,-190]</t>
+  </si>
+  <si>
+    <t>设置多关节，6关节超限（190）</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,190]</t>
+  </si>
+  <si>
+    <t>设置多关节，速度超限（0）</t>
+  </si>
+  <si>
+    <t>设置多关节，速度超限（101）</t>
   </si>
 </sst>
 </file>
@@ -936,6 +1048,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -943,9 +1058,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1277,18 +1389,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1307,8 +1419,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1335,18 +1447,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1358,15 +1470,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1393,18 +1505,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1416,15 +1528,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1443,8 +1555,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" ht="28.8" spans="1:6">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1456,7 +1568,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
@@ -1464,7 +1576,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1481,7 +1593,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1507,18 +1619,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1530,15 +1642,15 @@
       <c r="D1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1557,8 +1669,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" ht="28.8" spans="1:6">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1570,7 +1682,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -1587,18 +1699,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1610,15 +1722,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1637,8 +1749,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" ht="28.8" spans="1:6">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1650,7 +1762,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
@@ -1658,7 +1770,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1675,7 +1787,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1701,18 +1813,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1724,15 +1836,15 @@
       <c r="D1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1751,8 +1863,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" ht="28.8" spans="1:6">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1764,7 +1876,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -1781,19 +1893,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="20.125" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.775" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.775" customWidth="1"/>
+    <col min="4" max="4" width="20.1296296296296" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:7">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1808,15 +1920,15 @@
       <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:7">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:7">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1838,8 +1950,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:7">
-      <c r="A3" s="1">
+    <row r="3" ht="28.8" spans="1:7">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1851,7 +1963,7 @@
       <c r="D3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" s="10" t="s">
@@ -1872,32 +1984,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18" style="2" customWidth="1"/>
-    <col min="4" max="5" width="20.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.775" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.775" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.775" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.775" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="35.7777777777778" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="5" width="20.1296296296296" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" style="5" customWidth="1"/>
+    <col min="8" max="9" width="14.7777777777778" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F1" s="6" t="s">
@@ -1906,27 +2017,27 @@
       <c r="G1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:9">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="2" ht="28.8" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
         <v>168</v>
       </c>
       <c r="F2" s="6">
@@ -1935,815 +2046,1301 @@
       <c r="G2" s="6">
         <v>1</v>
       </c>
-      <c r="H2" s="5">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" ht="27" spans="1:9">
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" spans="1:9">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-168</v>
+      </c>
+      <c r="F3" s="4">
+        <v>20</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" spans="1:9">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>135</v>
+      </c>
+      <c r="F4" s="6">
+        <v>30</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="28.8" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8">
+        <v>-135</v>
+      </c>
+      <c r="F5" s="4">
+        <v>40</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" spans="1:9">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3">
+        <v>150</v>
+      </c>
+      <c r="F6" s="6">
+        <v>50</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" spans="1:9">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>-150</v>
+      </c>
+      <c r="F7" s="4">
+        <v>60</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="28.8" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>145</v>
+      </c>
+      <c r="F8" s="6">
+        <v>70</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:9">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-145</v>
+      </c>
+      <c r="F9" s="4">
+        <v>80</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:9">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>165</v>
+      </c>
+      <c r="F10" s="6">
+        <v>90</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:9">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-165</v>
+      </c>
+      <c r="F11" s="4">
+        <v>100</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="28.8" spans="1:9">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3">
+        <v>180</v>
+      </c>
+      <c r="F12" s="6">
+        <v>10</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:9">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-180</v>
+      </c>
+      <c r="F13" s="4">
+        <v>20</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" ht="28.8" spans="1:9">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>168</v>
+      </c>
+      <c r="F14" s="6">
+        <v>30</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="28.8" spans="1:9">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-168</v>
+      </c>
+      <c r="F15" s="4">
+        <v>40</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" ht="28.8" spans="1:9">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>135</v>
+      </c>
+      <c r="F16" s="6">
+        <v>50</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:9">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-135</v>
+      </c>
+      <c r="F17" s="4">
+        <v>60</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" ht="28.8" spans="1:9">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>150</v>
+      </c>
+      <c r="F18" s="6">
+        <v>70</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" ht="28.8" spans="1:9">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-150</v>
+      </c>
+      <c r="F19" s="4">
+        <v>80</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:9">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="3">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>145</v>
+      </c>
+      <c r="F20" s="6">
+        <v>90</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" spans="1:9">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="3">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-145</v>
+      </c>
+      <c r="F21" s="4">
+        <v>100</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:9">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>165</v>
+      </c>
+      <c r="F22" s="4">
+        <v>60</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" ht="28.8" spans="1:9">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-165</v>
+      </c>
+      <c r="F23" s="4">
+        <v>60</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" ht="28.8" spans="1:9">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="3">
+        <v>6</v>
+      </c>
+      <c r="E24" s="3">
+        <v>180</v>
+      </c>
+      <c r="F24" s="4">
+        <v>60</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" ht="28.8" spans="1:9">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="3">
+        <v>6</v>
+      </c>
+      <c r="E25" s="3">
+        <v>-180</v>
+      </c>
+      <c r="F25" s="4">
+        <v>60</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="3">
+        <v>7</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4">
+        <v>60</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <v>60</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>170</v>
+      </c>
+      <c r="F28" s="4">
+        <v>60</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-140</v>
+      </c>
+      <c r="F29" s="4">
+        <v>60</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>20</v>
+      </c>
+      <c r="F30" s="4">
+        <v>101</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>30</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="42.8888888888889" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.3333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.8148148148148" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.4444444444444" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.4259259259259" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>-168</v>
-      </c>
-      <c r="F3" s="3">
-        <v>20</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="27" spans="1:9">
+      <c r="B3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="1">
+        <v>50</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>135</v>
-      </c>
-      <c r="F4" s="6">
-        <v>30</v>
-      </c>
-      <c r="G4" s="6">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="27" spans="1:9">
-      <c r="A5" s="5">
+      <c r="B4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="1">
+        <v>100</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2</v>
-      </c>
-      <c r="E5" s="8">
-        <v>-135</v>
-      </c>
-      <c r="F5" s="3">
-        <v>40</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="27" spans="1:9">
+      <c r="B5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="2">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <v>150</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="B6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="1">
         <v>50</v>
       </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:9">
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1">
+        <v>100</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="1">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="1">
+        <v>50</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="1">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="1">
+        <v>50</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="1">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="1">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="1">
+        <v>50</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="1">
+        <v>50</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="1">
+        <v>50</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="1">
+        <v>50</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="1">
+        <v>50</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="1">
+        <v>50</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="1">
+        <v>101</v>
+      </c>
+      <c r="F21" s="1">
         <v>3</v>
       </c>
-      <c r="E7" s="2">
-        <v>-150</v>
-      </c>
-      <c r="F7" s="3">
-        <v>60</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" ht="27" spans="1:9">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4</v>
-      </c>
-      <c r="E8" s="2">
-        <v>145</v>
-      </c>
-      <c r="F8" s="6">
-        <v>70</v>
-      </c>
-      <c r="G8" s="6">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="1:9">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="2">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-145</v>
-      </c>
-      <c r="F9" s="3">
-        <v>80</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" ht="27" spans="1:9">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="2">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2">
-        <v>165</v>
-      </c>
-      <c r="F10" s="6">
-        <v>90</v>
-      </c>
-      <c r="G10" s="6">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="27" spans="1:9">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="2">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-165</v>
-      </c>
-      <c r="F11" s="3">
-        <v>100</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:9">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="2">
-        <v>6</v>
-      </c>
-      <c r="E12" s="2">
-        <v>180</v>
-      </c>
-      <c r="F12" s="6">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" ht="27" spans="1:9">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="2">
-        <v>6</v>
-      </c>
-      <c r="E13" s="2">
-        <v>-180</v>
-      </c>
-      <c r="F13" s="3">
-        <v>20</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" ht="27" spans="1:9">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5">
-        <v>168</v>
-      </c>
-      <c r="F14" s="6">
-        <v>30</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="27" spans="1:9">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5">
-        <v>-168</v>
-      </c>
-      <c r="F15" s="3">
-        <v>40</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" ht="27" spans="1:9">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2">
-        <v>135</v>
-      </c>
-      <c r="F16" s="6">
-        <v>50</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" ht="27" spans="1:9">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="2">
-        <v>2</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-135</v>
-      </c>
-      <c r="F17" s="3">
-        <v>60</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" ht="27" spans="1:9">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="2">
-        <v>3</v>
-      </c>
-      <c r="E18" s="2">
-        <v>150</v>
-      </c>
-      <c r="F18" s="6">
-        <v>70</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" ht="27" spans="1:9">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3</v>
-      </c>
-      <c r="E19" s="2">
-        <v>-150</v>
-      </c>
-      <c r="F19" s="3">
-        <v>80</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" ht="27" spans="1:9">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>145</v>
-      </c>
-      <c r="F20" s="6">
-        <v>90</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" ht="27" spans="1:9">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="2">
-        <v>4</v>
-      </c>
-      <c r="E21" s="2">
-        <v>-145</v>
-      </c>
-      <c r="F21" s="3">
-        <v>100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" ht="27" spans="1:9">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="2">
-        <v>5</v>
-      </c>
-      <c r="E22" s="2">
-        <v>165</v>
-      </c>
-      <c r="F22" s="3">
-        <v>60</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5">
-        <v>1</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" ht="27" spans="1:9">
-      <c r="A23" s="5">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="2">
-        <v>5</v>
-      </c>
-      <c r="E23" s="2">
-        <v>-165</v>
-      </c>
-      <c r="F23" s="3">
-        <v>60</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5">
-        <v>1</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="27" spans="1:9">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="2">
-        <v>6</v>
-      </c>
-      <c r="E24" s="2">
-        <v>180</v>
-      </c>
-      <c r="F24" s="3">
-        <v>60</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" ht="27" spans="1:9">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="2">
-        <v>6</v>
-      </c>
-      <c r="E25" s="2">
-        <v>-180</v>
-      </c>
-      <c r="F25" s="3">
-        <v>60</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="2">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>60</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>60</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2">
-        <v>170</v>
-      </c>
-      <c r="F28" s="3">
-        <v>60</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="2">
-        <v>2</v>
-      </c>
-      <c r="E29" s="2">
-        <v>-140</v>
-      </c>
-      <c r="F29" s="3">
-        <v>60</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2">
-        <v>20</v>
-      </c>
-      <c r="F30" s="3">
-        <v>101</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1</v>
-      </c>
-      <c r="E31" s="2">
-        <v>30</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2757,18 +3354,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -2780,15 +3377,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -2816,18 +3413,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -2839,15 +3436,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -2875,18 +3472,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="19.125" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="19.1296296296296" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -2898,15 +3495,15 @@
       <c r="D1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="43.2" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -2925,8 +3522,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" ht="28.8" spans="1:6">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2938,7 +3535,7 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -2955,18 +3552,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -2978,15 +3575,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -3013,20 +3610,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.775" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.6296296296296" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -3038,21 +3635,21 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="40.5" spans="1:8">
-      <c r="A2" s="5">
+    <row r="2" ht="43.2" spans="1:8">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -3065,18 +3662,18 @@
       <c r="E2" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
         <v>1</v>
       </c>
       <c r="H2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" ht="40.5" spans="1:8">
-      <c r="A3" s="1">
+    <row r="3" ht="43.2" spans="1:8">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -3088,10 +3685,10 @@
       <c r="E3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
@@ -3108,20 +3705,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.775" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.6296296296296" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -3133,21 +3730,21 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="40.5" spans="1:8">
-      <c r="A2" s="5">
+    <row r="2" ht="43.2" spans="1:8">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -3160,18 +3757,18 @@
       <c r="E2" s="6">
         <v>-1</v>
       </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
         <v>-1</v>
       </c>
       <c r="H2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="40.5" spans="1:8">
-      <c r="A3" s="1">
+    <row r="3" customFormat="1" ht="43.2" spans="1:8">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -3183,10 +3780,10 @@
       <c r="E3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
         <v>-1</v>
       </c>
       <c r="H3" t="s">
@@ -3203,18 +3800,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -3226,15 +3823,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="43.2" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -3251,8 +3848,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="27" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" customFormat="1" ht="43.2" spans="1:6">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -3278,18 +3875,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.775" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -3301,15 +3898,15 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="5">
+    <row r="2" ht="28.8" spans="1:6">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">

--- a/test_data/mycobot_280.xlsx
+++ b/test_data/mycobot_280.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="10" activeTab="16"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="10" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="get_modify_version" sheetId="4" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="get_angles" sheetId="3" r:id="rId15"/>
     <sheet name="send_angle" sheetId="16" r:id="rId16"/>
     <sheet name="send_angles" sheetId="17" r:id="rId17"/>
+    <sheet name="get_coords" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="130">
   <si>
     <t>ID</t>
   </si>
@@ -418,6 +419,21 @@
   </si>
   <si>
     <t>设置多关节，速度超限（101）</t>
+  </si>
+  <si>
+    <t>coords</t>
+  </si>
+  <si>
+    <t>刷新模式下获取坐标</t>
+  </si>
+  <si>
+    <t>[170,-62,230,179,0,-90]</t>
+  </si>
+  <si>
+    <t>插补模式下获取坐标</t>
+  </si>
+  <si>
+    <t>[170,-20,230,179,0,-90]</t>
   </si>
 </sst>
 </file>
@@ -1047,32 +1063,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1391,28 +1407,28 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="5" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1420,16 +1436,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6">
         <v>7</v>
       </c>
@@ -1449,28 +1465,28 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1478,16 +1494,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6">
         <v>1</v>
       </c>
@@ -1507,28 +1523,28 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1536,16 +1552,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="6">
@@ -1556,10 +1572,10 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C3" t="s">
@@ -1568,7 +1584,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" t="s">
@@ -1576,7 +1592,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1593,7 +1609,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1621,28 +1637,28 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1650,16 +1666,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="6">
@@ -1670,10 +1686,10 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C3" t="s">
@@ -1682,7 +1698,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -1701,28 +1717,28 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1730,16 +1746,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C2" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="6">
@@ -1750,10 +1766,10 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C3" t="s">
@@ -1762,7 +1778,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" t="s">
@@ -1770,7 +1786,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1787,7 +1803,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1815,28 +1831,28 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1844,16 +1860,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="6">
@@ -1864,10 +1880,10 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C3" t="s">
@@ -1876,7 +1892,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -1895,32 +1911,32 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="20.1296296296296" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
@@ -1928,22 +1944,22 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:7">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="4" t="s">
         <v>54</v>
       </c>
       <c r="G2" t="s">
@@ -1951,7 +1967,7 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:7">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1960,13 +1976,13 @@
       <c r="C3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G3" t="s">
@@ -1986,58 +2002,58 @@
   <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.7777777777778" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18" style="3" customWidth="1"/>
-    <col min="4" max="5" width="20.1296296296296" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.7777777777778" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.7777777777778" style="5" customWidth="1"/>
-    <col min="8" max="9" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="5" width="20.1296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" style="2" customWidth="1"/>
+    <col min="8" max="9" width="14.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:9">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
         <v>168</v>
       </c>
       <c r="F2" s="6">
@@ -2046,56 +2062,56 @@
       <c r="G2" s="6">
         <v>1</v>
       </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:9">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
         <v>-168</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="7">
         <v>20</v>
       </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="G3" s="7">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="28.8" spans="1:9">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <v>135</v>
       </c>
       <c r="F4" s="6">
@@ -2104,56 +2120,56 @@
       <c r="G4" s="6">
         <v>1</v>
       </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:9">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="9">
         <v>-135</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="7">
         <v>40</v>
       </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="28.8" spans="1:9">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>3</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>150</v>
       </c>
       <c r="F6" s="6">
@@ -2162,56 +2178,56 @@
       <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="28.8" spans="1:9">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>3</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>-150</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="7">
         <v>60</v>
       </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:9">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>145</v>
       </c>
       <c r="F8" s="6">
@@ -2220,56 +2236,56 @@
       <c r="G8" s="6">
         <v>1</v>
       </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:9">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="1">
         <v>4</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>-145</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="7">
         <v>80</v>
       </c>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:9">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="1">
         <v>5</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
         <v>165</v>
       </c>
       <c r="F10" s="6">
@@ -2278,56 +2294,56 @@
       <c r="G10" s="6">
         <v>1</v>
       </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:9">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>-165</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="7">
         <v>100</v>
       </c>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="G11" s="7">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:9">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="1">
         <v>6</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>180</v>
       </c>
       <c r="F12" s="6">
@@ -2336,56 +2352,56 @@
       <c r="G12" s="6">
         <v>1</v>
       </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:9">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
         <v>6</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>-180</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="7">
         <v>20</v>
       </c>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="G13" s="7">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:9">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
         <v>168</v>
       </c>
       <c r="F14" s="6">
@@ -2394,56 +2410,56 @@
       <c r="G14" s="6">
         <v>0</v>
       </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" ht="28.8" spans="1:9">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
         <v>-168</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="7">
         <v>40</v>
       </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:9">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
         <v>135</v>
       </c>
       <c r="F16" s="6">
@@ -2452,56 +2468,56 @@
       <c r="G16" s="6">
         <v>0</v>
       </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" ht="28.8" spans="1:9">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="1">
         <v>2</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <v>-135</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="7">
         <v>60</v>
       </c>
-      <c r="G17" s="4">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" ht="28.8" spans="1:9">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>3</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>150</v>
       </c>
       <c r="F18" s="6">
@@ -2510,56 +2526,56 @@
       <c r="G18" s="6">
         <v>0</v>
       </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" ht="28.8" spans="1:9">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="1">
         <v>3</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="1">
         <v>-150</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="7">
         <v>80</v>
       </c>
-      <c r="G19" s="4">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>1</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" ht="28.8" spans="1:9">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="1">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="1">
         <v>145</v>
       </c>
       <c r="F20" s="6">
@@ -2568,293 +2584,293 @@
       <c r="G20" s="6">
         <v>0</v>
       </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" ht="28.8" spans="1:9">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="1">
         <v>4</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="1">
         <v>-145</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="7">
         <v>100</v>
       </c>
-      <c r="G21" s="4">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" ht="28.8" spans="1:9">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="1">
         <v>5</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="1">
         <v>165</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="7">
         <v>60</v>
       </c>
       <c r="G22" s="6">
         <v>0</v>
       </c>
-      <c r="H22" s="2">
-        <v>1</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" ht="28.8" spans="1:9">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="1">
         <v>5</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="1">
         <v>-165</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="7">
         <v>60</v>
       </c>
-      <c r="G23" s="4">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>1</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="G23" s="7">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" ht="28.8" spans="1:9">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="1">
         <v>6</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="1">
         <v>180</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="7">
         <v>60</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
       </c>
-      <c r="H24" s="2">
-        <v>1</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" ht="28.8" spans="1:9">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="1">
         <v>6</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="1">
         <v>-180</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="7">
         <v>60</v>
       </c>
-      <c r="G25" s="4">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="G25" s="7">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="1">
         <v>7</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4">
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7">
         <v>60</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="3">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4">
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7">
         <v>60</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
         <v>170</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="7">
         <v>60</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="1">
         <v>-140</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="7">
         <v>60</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
         <v>20</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="7">
         <v>101</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
         <v>30</v>
       </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="F31" s="7">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2870,478 +2886,568 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="42.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8148148148148" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.4259259259259" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="8"/>
+    <col min="2" max="2" width="42.8888888888889" style="8" customWidth="1"/>
+    <col min="3" max="3" width="15.5555555555556" style="8" customWidth="1"/>
+    <col min="4" max="4" width="34.3333333333333" style="8" customWidth="1"/>
+    <col min="5" max="5" width="11.8148148148148" style="8" customWidth="1"/>
+    <col min="6" max="7" width="13.4444444444444" style="8" customWidth="1"/>
+    <col min="8" max="8" width="15.4259259259259" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="8.88888888888889" style="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="8">
         <v>10</v>
       </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="8">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8">
+        <v>1</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="8">
+        <v>50</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="8">
+        <v>100</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="8">
+        <v>10</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="8">
+        <v>50</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="8">
+        <v>100</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="8">
+        <v>50</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="8">
+        <v>50</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="8">
+        <v>50</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="8">
+        <v>50</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="8">
+        <v>50</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="8">
+        <v>50</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="8">
+        <v>50</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="8">
+        <v>50</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="8">
+        <v>50</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="8">
+        <v>50</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="8">
+        <v>50</v>
+      </c>
+      <c r="F18" s="8">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="8">
+        <v>50</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8">
+        <v>2</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="8">
+        <v>101</v>
+      </c>
+      <c r="F21" s="8">
+        <v>3</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="27.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" spans="1:7">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28.8" spans="1:7">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" spans="1:7">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="1">
-        <v>50</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" s="1">
-        <v>100</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="1">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="1">
-        <v>50</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="1">
-        <v>100</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="1">
-        <v>50</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="1">
-        <v>50</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="1">
-        <v>50</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="1">
-        <v>50</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="1">
-        <v>50</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="1">
-        <v>50</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="1">
-        <v>50</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="1">
-        <v>50</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="1">
-        <v>50</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="1">
-        <v>50</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="1">
-        <v>50</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" s="1">
-        <v>50</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="1">
-        <v>101</v>
-      </c>
-      <c r="F21" s="1">
-        <v>3</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>39</v>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3356,28 +3462,28 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3385,16 +3491,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="11">
         <v>7.2</v>
       </c>
@@ -3415,28 +3521,28 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3444,16 +3550,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="11">
         <v>2.4</v>
       </c>
@@ -3474,28 +3580,28 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="19.1296296296296" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3503,16 +3609,16 @@
       </c>
     </row>
     <row r="2" ht="43.2" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="6">
@@ -3523,10 +3629,10 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
@@ -3535,7 +3641,7 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -3554,28 +3660,28 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3583,16 +3689,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6">
         <v>1</v>
       </c>
@@ -3612,36 +3718,36 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.6296296296296" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6296296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
@@ -3649,23 +3755,23 @@
       </c>
     </row>
     <row r="2" ht="43.2" spans="1:8">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2" t="s">
@@ -3673,10 +3779,10 @@
       </c>
     </row>
     <row r="3" ht="43.2" spans="1:8">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
@@ -3685,10 +3791,10 @@
       <c r="E3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
         <v>1</v>
       </c>
       <c r="H3" t="s">
@@ -3707,36 +3813,36 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.6296296296296" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6296296296296" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
@@ -3744,23 +3850,23 @@
       </c>
     </row>
     <row r="2" ht="43.2" spans="1:8">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6">
         <v>-1</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
         <v>-1</v>
       </c>
       <c r="H2" t="s">
@@ -3768,10 +3874,10 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C3" t="s">
@@ -3780,10 +3886,10 @@
       <c r="E3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
         <v>-1</v>
       </c>
       <c r="H3" t="s">
@@ -3802,28 +3908,28 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3831,16 +3937,16 @@
       </c>
     </row>
     <row r="2" ht="43.2" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6">
         <v>1</v>
       </c>
@@ -3849,10 +3955,10 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="43.2" spans="1:6">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C3" t="s">
@@ -3877,28 +3983,28 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="20.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -3906,16 +4012,16 @@
       </c>
     </row>
     <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="6">
         <v>1</v>
       </c>

--- a/test_data/mycobot_280.xlsx
+++ b/test_data/mycobot_280.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="21" activeTab="32"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="21" activeTab="32"/>
   </bookViews>
   <sheets>
     <sheet name="get_modify_version" sheetId="4" r:id="rId1"/>

--- a/test_data/mycobot_280.xlsx
+++ b/test_data/mycobot_280.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="21" activeTab="32"/>
+    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="44" activeTab="51"/>
   </bookViews>
   <sheets>
     <sheet name="get_modify_version" sheetId="4" r:id="rId1"/>
@@ -40,6 +40,25 @@
     <sheet name="jog_coord" sheetId="31" r:id="rId31"/>
     <sheet name="jog_increment_angle" sheetId="32" r:id="rId32"/>
     <sheet name="jog_increment_coord" sheetId="33" r:id="rId33"/>
+    <sheet name="set_hts_gripper_torque" sheetId="34" r:id="rId34"/>
+    <sheet name="get_hts_gripper_torque" sheetId="35" r:id="rId35"/>
+    <sheet name="set_gripper_protect_current" sheetId="36" r:id="rId36"/>
+    <sheet name="get_gripper_protect_current" sheetId="37" r:id="rId37"/>
+    <sheet name="set_encoder" sheetId="38" r:id="rId38"/>
+    <sheet name="get_encoder" sheetId="39" r:id="rId39"/>
+    <sheet name="set_encoders" sheetId="40" r:id="rId40"/>
+    <sheet name="get_encoders" sheetId="41" r:id="rId41"/>
+    <sheet name="get_joint_max_angle" sheetId="42" r:id="rId42"/>
+    <sheet name="get_joint_min_angle" sheetId="43" r:id="rId43"/>
+    <sheet name="set_joint_max" sheetId="44" r:id="rId44"/>
+    <sheet name="set_joint_min" sheetId="45" r:id="rId45"/>
+    <sheet name="is_servo_enable" sheetId="46" r:id="rId46"/>
+    <sheet name="is_all_servo_enable" sheetId="47" r:id="rId47"/>
+    <sheet name="set_servo_calibration" sheetId="48" r:id="rId48"/>
+    <sheet name="joint_brake" sheetId="49" r:id="rId49"/>
+    <sheet name="release_servo" sheetId="50" r:id="rId50"/>
+    <sheet name="focus_servo" sheetId="51" r:id="rId51"/>
+    <sheet name="set_gripper_state" sheetId="52" r:id="rId52"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="482">
   <si>
     <t>ID</t>
   </si>
@@ -1118,6 +1137,393 @@
   </si>
   <si>
     <t>设置x轴增量超限</t>
+  </si>
+  <si>
+    <t>正常设置自适应夹爪扭矩</t>
+  </si>
+  <si>
+    <t>set_hts_gripper_torque</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪扭矩超限</t>
+  </si>
+  <si>
+    <t>正常获取自适应夹爪扭矩默认值</t>
+  </si>
+  <si>
+    <t>正常设置自适应夹爪电流</t>
+  </si>
+  <si>
+    <t>set_gripper_protect_current</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪电流超限</t>
+  </si>
+  <si>
+    <t>正常获取自适应夹爪夹持电流默认值</t>
+  </si>
+  <si>
+    <t>encoder</t>
+  </si>
+  <si>
+    <t>set_encoder</t>
+  </si>
+  <si>
+    <t>正常获取一关节电位值</t>
+  </si>
+  <si>
+    <t>get_encoder</t>
+  </si>
+  <si>
+    <t>正常获取二关节电位值</t>
+  </si>
+  <si>
+    <t>正常获取三关节电位值</t>
+  </si>
+  <si>
+    <t>正常获取四关节电位值</t>
+  </si>
+  <si>
+    <t>正常获取五关节电位值</t>
+  </si>
+  <si>
+    <t>正常获取六关节电位值</t>
+  </si>
+  <si>
+    <t>获取关节电位值，关节超限</t>
+  </si>
+  <si>
+    <t>encoders</t>
+  </si>
+  <si>
+    <t>[3947,2048,2048,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[150,2048,2048,2048,2048,2048</t>
+  </si>
+  <si>
+    <t>[2048,3574,1024,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,523,3000,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,3743,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,353,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,3687,1024,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,410,1024,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,3913,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,184,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,2048,4082]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,2048,14]</t>
+  </si>
+  <si>
+    <t>[4097,2048,2048,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[-1,2048,2048,2048,2048,2048</t>
+  </si>
+  <si>
+    <t>[2048,4097,1024,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,-1,3000,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,4097,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,-1,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,4097,1024,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,-1,1024,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,4097,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,-1,2048]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,2048,4097]</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,2048,-1]</t>
+  </si>
+  <si>
+    <t>正常获取全关节电位值-零位</t>
+  </si>
+  <si>
+    <t>get_encoders</t>
+  </si>
+  <si>
+    <t>[2048,2048,2048,2048,2048,2048]</t>
+  </si>
+  <si>
+    <t>获取1关节最大角度</t>
+  </si>
+  <si>
+    <t>get_joint_max_angle</t>
+  </si>
+  <si>
+    <t>获取2关节最大角度</t>
+  </si>
+  <si>
+    <t>获取3关节最大角度</t>
+  </si>
+  <si>
+    <t>获取4关节最大角度</t>
+  </si>
+  <si>
+    <t>获取5关节最大角度</t>
+  </si>
+  <si>
+    <t>获取6关节最大角度</t>
+  </si>
+  <si>
+    <t>获取关节超限</t>
+  </si>
+  <si>
+    <t>获取1关节最小角度</t>
+  </si>
+  <si>
+    <t>get_joint_min_angle</t>
+  </si>
+  <si>
+    <t>获取2关节最小角度</t>
+  </si>
+  <si>
+    <t>获取3关节最小角度</t>
+  </si>
+  <si>
+    <t>获取4关节最小角度</t>
+  </si>
+  <si>
+    <t>获取5关节最小角度</t>
+  </si>
+  <si>
+    <t>获取6关节最小角度</t>
+  </si>
+  <si>
+    <t>设置一关节最大角度</t>
+  </si>
+  <si>
+    <t>set_joint_max</t>
+  </si>
+  <si>
+    <t>设置二关节最大角度</t>
+  </si>
+  <si>
+    <t>设置三关节最大角度</t>
+  </si>
+  <si>
+    <t>设置四关节最大角度</t>
+  </si>
+  <si>
+    <t>设置五关节最大角度</t>
+  </si>
+  <si>
+    <t>设置六关节最大角度</t>
+  </si>
+  <si>
+    <t>设置1关节角度超限</t>
+  </si>
+  <si>
+    <t>设置2关节角度超限</t>
+  </si>
+  <si>
+    <t>设置3关节角度超限</t>
+  </si>
+  <si>
+    <t>设置4关节角度超限</t>
+  </si>
+  <si>
+    <t>设置5关节角度超限</t>
+  </si>
+  <si>
+    <t>设置6关节角度超限</t>
+  </si>
+  <si>
+    <t>设置一关节最小角度</t>
+  </si>
+  <si>
+    <t>set_joint_min</t>
+  </si>
+  <si>
+    <t>设置二关节最小角度</t>
+  </si>
+  <si>
+    <t>设置三关节最小角度</t>
+  </si>
+  <si>
+    <t>设置四关节最小角度</t>
+  </si>
+  <si>
+    <t>设置五关节最小角度</t>
+  </si>
+  <si>
+    <t>设置六关节最小角度</t>
+  </si>
+  <si>
+    <t>获取1关节连接状态</t>
+  </si>
+  <si>
+    <t>is_servo_enable</t>
+  </si>
+  <si>
+    <t>获取2关节连接状态</t>
+  </si>
+  <si>
+    <t>获取3关节连接状态</t>
+  </si>
+  <si>
+    <t>获取4关节连接状态</t>
+  </si>
+  <si>
+    <t>获取5关节连接状态</t>
+  </si>
+  <si>
+    <t>获取6关节连接状态</t>
+  </si>
+  <si>
+    <t>正常全关节连接状态</t>
+  </si>
+  <si>
+    <t>is_all_servo_enable</t>
+  </si>
+  <si>
+    <t>设置一关节零位</t>
+  </si>
+  <si>
+    <t>set_servo_calibration</t>
+  </si>
+  <si>
+    <t>设置二关节零位</t>
+  </si>
+  <si>
+    <t>设置三关节零位</t>
+  </si>
+  <si>
+    <t>设置四关节零位</t>
+  </si>
+  <si>
+    <t>设置五关节零位</t>
+  </si>
+  <si>
+    <t>设置六关节零位</t>
+  </si>
+  <si>
+    <t>设置一关节刹车开关</t>
+  </si>
+  <si>
+    <t>set_break</t>
+  </si>
+  <si>
+    <t>设置二关节刹车开关</t>
+  </si>
+  <si>
+    <t>设置三关节刹车开关</t>
+  </si>
+  <si>
+    <t>设置四关节刹车开关</t>
+  </si>
+  <si>
+    <t>设置五关节刹车开关</t>
+  </si>
+  <si>
+    <t>设置六关节刹车开关</t>
+  </si>
+  <si>
+    <t>设置开关状态超限</t>
+  </si>
+  <si>
+    <t>使1关节掉电</t>
+  </si>
+  <si>
+    <t>release_servo</t>
+  </si>
+  <si>
+    <t>使2关节掉电</t>
+  </si>
+  <si>
+    <t>使3关节掉电</t>
+  </si>
+  <si>
+    <t>使4关节掉电</t>
+  </si>
+  <si>
+    <t>使5关节掉电</t>
+  </si>
+  <si>
+    <t>使6关节掉电</t>
+  </si>
+  <si>
+    <t>使1关节上电</t>
+  </si>
+  <si>
+    <t>focus_servo</t>
+  </si>
+  <si>
+    <t>使2关节上电</t>
+  </si>
+  <si>
+    <t>使3关节上电</t>
+  </si>
+  <si>
+    <t>使4关节上电</t>
+  </si>
+  <si>
+    <t>使5关节上电</t>
+  </si>
+  <si>
+    <t>使6关节上电</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>is_torque</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪（力控）张开</t>
+  </si>
+  <si>
+    <t>set_gripper_state</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪（力控）闭合</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪（力控）释放</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪（力控）状态超限</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪（力控）速度超限</t>
+  </si>
+  <si>
+    <t>设置自适应夹爪（力控）为非力控模式</t>
   </si>
 </sst>
 </file>
@@ -1747,20 +2153,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2085,11 +2491,11 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2106,7 +2512,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -2124,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>2</v>
       </c>
       <c r="F2" t="s">
@@ -2143,11 +2549,11 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2182,7 +2588,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">
@@ -2201,11 +2607,11 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2242,7 +2648,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">
@@ -2250,7 +2656,7 @@
       </c>
     </row>
     <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2262,7 +2668,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" t="s">
@@ -2270,7 +2676,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -2287,7 +2693,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -2315,11 +2721,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2356,7 +2762,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">
@@ -2364,7 +2770,7 @@
       </c>
     </row>
     <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2376,7 +2782,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -2395,11 +2801,11 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2436,7 +2842,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">
@@ -2444,7 +2850,7 @@
       </c>
     </row>
     <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2456,7 +2862,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" t="s">
@@ -2464,7 +2870,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -2481,7 +2887,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -2509,11 +2915,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2550,7 +2956,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">
@@ -2558,7 +2964,7 @@
       </c>
     </row>
     <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2570,7 +2976,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -2589,12 +2995,12 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="20.1333333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="7" customWidth="1"/>
-    <col min="6" max="6" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="6" max="6" width="14.775" style="4" customWidth="1"/>
     <col min="7" max="7" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2611,7 +3017,7 @@
       <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -2634,7 +3040,7 @@
       <c r="D2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2645,7 +3051,7 @@
       </c>
     </row>
     <row r="3" ht="27" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2657,7 +3063,7 @@
       <c r="D3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="5">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2680,13 +3086,13 @@
   <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
-    <col min="2" max="2" width="35.775" style="6" customWidth="1"/>
-    <col min="3" max="3" width="18" style="6" customWidth="1"/>
-    <col min="4" max="5" width="20.1333333333333" style="6" customWidth="1"/>
-    <col min="6" max="6" width="14.775" style="8" customWidth="1"/>
-    <col min="7" max="7" width="14.775" style="7" customWidth="1"/>
-    <col min="8" max="9" width="14.775" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
+    <col min="2" max="2" width="35.775" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="5" width="20.1333333333333" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.775" style="5" customWidth="1"/>
+    <col min="7" max="7" width="14.775" style="6" customWidth="1"/>
+    <col min="8" max="9" width="14.775" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:9">
@@ -2705,16 +3111,16 @@
       <c r="E1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2725,7 +3131,7 @@
       <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="2">
@@ -2734,27 +3140,27 @@
       <c r="E2" s="2">
         <v>168</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="7">
         <v>10</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="7">
         <v>1</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="2">
@@ -2763,45 +3169,45 @@
       <c r="E3" s="2">
         <v>-168</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="5">
         <v>20</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>135</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="7">
         <v>30</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="7">
         <v>1</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2812,83 +3218,83 @@
       <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="9">
         <v>-135</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="5">
         <v>40</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>3</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>150</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="7">
         <v>50</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="7">
         <v>1</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>-150</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="5">
         <v>60</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="5">
         <v>1</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2899,54 +3305,54 @@
       <c r="B8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>4</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>145</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="7">
         <v>70</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="7">
         <v>1</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>4</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>-145</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="5">
         <v>80</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="5">
         <v>1</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2957,83 +3363,83 @@
       <c r="B10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>5</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>160</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="7">
         <v>90</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="7">
         <v>1</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>5</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>-155</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="5">
         <v>100</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="5">
         <v>1</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>6</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>180</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <v>10</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="7">
         <v>1</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3044,36 +3450,36 @@
       <c r="B13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>6</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>-180</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="5">
         <v>20</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="5">
         <v>1</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="2">
@@ -3082,27 +3488,27 @@
       <c r="E14" s="2">
         <v>168</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>30</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="7">
         <v>0</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="2">
@@ -3111,16 +3517,16 @@
       <c r="E15" s="2">
         <v>-168</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="5">
         <v>40</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="5">
         <v>0</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3131,54 +3537,54 @@
       <c r="B16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="4">
         <v>2</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="4">
         <v>135</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="7">
         <v>50</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="7">
         <v>0</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="4">
         <v>2</v>
       </c>
       <c r="E17" s="10">
         <v>-135</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="5">
         <v>60</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="5">
         <v>0</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3189,83 +3595,83 @@
       <c r="B18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="4">
         <v>3</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="4">
         <v>150</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
         <v>70</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="7">
         <v>0</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="4">
         <v>3</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="4">
         <v>-150</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="5">
         <v>80</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="5">
         <v>0</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="4">
         <v>4</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="4">
         <v>145</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="7">
         <v>90</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="7">
         <v>0</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3276,83 +3682,83 @@
       <c r="B21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="4">
         <v>4</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="4">
         <v>-145</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="5">
         <v>100</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="5">
         <v>0</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="4">
         <v>5</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="4">
         <v>160</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="5">
         <v>60</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="7">
         <v>0</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="4">
         <v>5</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="4">
         <v>-155</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="5">
         <v>60</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="5">
         <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3363,54 +3769,54 @@
       <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="4">
         <v>6</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="4">
         <v>180</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="5">
         <v>60</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="7">
         <v>0</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="4">
         <v>6</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="4">
         <v>-180</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="5">
         <v>60</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="5">
         <v>0</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3418,68 +3824,68 @@
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="4">
         <v>7</v>
       </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="8">
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
         <v>60</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="6">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="8">
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
         <v>60</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="6">
-        <v>1</v>
-      </c>
-      <c r="E28" s="6">
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4">
         <v>20</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="5">
         <v>101</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3487,33 +3893,33 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6">
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
         <v>30</v>
       </c>
-      <c r="F29" s="8">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="s">
+      <c r="F29" s="5">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="2">
@@ -3522,23 +3928,23 @@
       <c r="E30" s="2">
         <v>169</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="7">
         <v>10</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="7"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D31" s="2">
@@ -3547,12 +3953,12 @@
       <c r="E31" s="2">
         <v>-169</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="5">
         <v>20</v>
       </c>
-      <c r="G31" s="8"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3563,46 +3969,46 @@
       <c r="B32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="4">
         <v>136</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="7">
         <v>30</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32" s="7"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="4">
         <v>2</v>
       </c>
       <c r="E33" s="9">
         <v>-136</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="5">
         <v>40</v>
       </c>
-      <c r="G33" s="8"/>
+      <c r="G33" s="5"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3613,71 +4019,71 @@
       <c r="B34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="4">
         <v>151</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="7">
         <v>50</v>
       </c>
-      <c r="G34" s="5"/>
+      <c r="G34" s="7"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="4">
         <v>3</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="4">
         <v>-151</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="5">
         <v>60</v>
       </c>
-      <c r="G35" s="8"/>
+      <c r="G35" s="5"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="6">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="4">
         <v>4</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="4">
         <v>146</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="7">
         <v>70</v>
       </c>
-      <c r="G36" s="5"/>
+      <c r="G36" s="7"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3688,71 +4094,71 @@
       <c r="B37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="4">
         <v>4</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="4">
         <v>-146</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="5">
         <v>80</v>
       </c>
-      <c r="G37" s="8"/>
+      <c r="G37" s="5"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="6">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="4">
         <v>5</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="4">
         <v>161</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="7">
         <v>90</v>
       </c>
-      <c r="G38" s="5"/>
+      <c r="G38" s="7"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="6">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="4">
         <v>5</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="4">
         <v>-156</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="5">
         <v>100</v>
       </c>
-      <c r="G39" s="8"/>
+      <c r="G39" s="5"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3763,46 +4169,46 @@
       <c r="B40" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="4">
         <v>6</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="4">
         <v>181</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="7">
         <v>10</v>
       </c>
-      <c r="G40" s="5"/>
+      <c r="G40" s="7"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="4">
         <v>6</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="4">
         <v>-181</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="5">
         <v>20</v>
       </c>
-      <c r="G41" s="8"/>
+      <c r="G41" s="5"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3818,14 +4224,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="8.89166666666667" style="6"/>
-    <col min="2" max="2" width="42.8916666666667" style="6" customWidth="1"/>
-    <col min="3" max="3" width="15.5583333333333" style="6" customWidth="1"/>
-    <col min="4" max="4" width="34.3333333333333" style="6" customWidth="1"/>
-    <col min="5" max="5" width="11.8166666666667" style="6" customWidth="1"/>
-    <col min="6" max="7" width="13.4416666666667" style="6" customWidth="1"/>
-    <col min="8" max="8" width="15.425" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="8.89166666666667" style="6"/>
+    <col min="1" max="1" width="8.89166666666667" style="4"/>
+    <col min="2" max="2" width="42.8916666666667" style="4" customWidth="1"/>
+    <col min="3" max="3" width="15.5583333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="34.3333333333333" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.8166666666667" style="4" customWidth="1"/>
+    <col min="6" max="7" width="13.4416666666667" style="4" customWidth="1"/>
+    <col min="8" max="8" width="15.425" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="8.89166666666667" style="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8">
@@ -3838,497 +4244,497 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>10</v>
       </c>
-      <c r="F2" s="6">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>50</v>
       </c>
-      <c r="F3" s="6">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>100</v>
       </c>
-      <c r="F4" s="6">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>10</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>50</v>
       </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>100</v>
       </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>50</v>
       </c>
-      <c r="F8" s="6">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="s">
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>50</v>
       </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>50</v>
       </c>
-      <c r="F10" s="6">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="s">
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>50</v>
       </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>50</v>
       </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="s">
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>50</v>
       </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="s">
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>50</v>
       </c>
-      <c r="F14" s="6">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6" t="s">
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="6">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>50</v>
       </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="6">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="4">
         <v>50</v>
       </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6" t="s">
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="4">
         <v>50</v>
       </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="H17" s="6" t="s">
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="4">
         <v>50</v>
       </c>
-      <c r="F18" s="6">
-        <v>1</v>
-      </c>
-      <c r="H18" s="6" t="s">
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="4">
         <v>50</v>
       </c>
-      <c r="F19" s="6">
-        <v>1</v>
-      </c>
-      <c r="H19" s="6" t="s">
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="4">
         <v>101</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="4">
         <v>3</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4344,13 +4750,13 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="26.125" customWidth="1"/>
-    <col min="5" max="5" width="25.125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="14.775" style="7" customWidth="1"/>
-    <col min="7" max="7" width="45.625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="25.125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="14.775" style="6" customWidth="1"/>
+    <col min="7" max="7" width="45.625" style="4" customWidth="1"/>
     <col min="8" max="8" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4367,10 +4773,10 @@
       <c r="D1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -4393,8 +4799,8 @@
       <c r="D2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -4405,7 +4811,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:8">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -4417,8 +4823,8 @@
       <c r="D3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5">
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -4429,7 +4835,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -4438,7 +4844,7 @@
       <c r="C4" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>143</v>
       </c>
       <c r="G4" t="s">
@@ -5315,11 +5721,11 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6133,7 +6539,7 @@
     <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.1333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="8" customWidth="1"/>
     <col min="6" max="6" width="14.775" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.775" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
@@ -6152,7 +6558,7 @@
       <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -6172,7 +6578,7 @@
       <c r="C2" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
@@ -6190,7 +6596,7 @@
       <c r="C3" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="7">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
@@ -6214,7 +6620,7 @@
     <col min="2" max="2" width="16.1083333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.1333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="8" customWidth="1"/>
     <col min="6" max="6" width="14.775" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.775" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
@@ -6233,7 +6639,7 @@
       <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -6254,7 +6660,7 @@
         <v>205</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -6275,7 +6681,7 @@
         <v>205</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="5">
+      <c r="E3" s="7">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -7829,11 +8235,11 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10834,17 +11240,1711 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="5" width="22.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D2" s="1">
+        <v>980</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D3" s="1">
+        <v>300</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:6">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D4" s="3">
+        <v>981</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="27" spans="1:6">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D5" s="3">
+        <v>149</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="5" width="22.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1">
+        <v>300</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="5" width="22.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" s="1">
+        <v>200</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D3" s="1">
+        <v>500</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D4" s="3">
+        <v>501</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="1" ht="27" spans="1:6">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="5" width="22.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E2" s="1">
+        <v>300</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
+    <col min="2" max="2" width="35.775" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="5" width="20.1333333333333" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.775" style="5" customWidth="1"/>
+    <col min="7" max="7" width="14.775" style="6" customWidth="1"/>
+    <col min="8" max="9" width="14.775" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3947</v>
+      </c>
+      <c r="F2" s="7">
+        <v>10</v>
+      </c>
+      <c r="G2" s="7">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>150</v>
+      </c>
+      <c r="F3" s="5">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3574</v>
+      </c>
+      <c r="F4" s="7">
+        <v>30</v>
+      </c>
+      <c r="G4" s="7">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>523</v>
+      </c>
+      <c r="F5" s="5">
+        <v>40</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3743</v>
+      </c>
+      <c r="F6" s="7">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>353</v>
+      </c>
+      <c r="F7" s="5">
+        <v>60</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3687</v>
+      </c>
+      <c r="F8" s="7">
+        <v>70</v>
+      </c>
+      <c r="G8" s="7">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="4">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>410</v>
+      </c>
+      <c r="F9" s="5">
+        <v>80</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D10" s="4">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2225</v>
+      </c>
+      <c r="F10" s="7">
+        <v>90</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D11" s="4">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>184</v>
+      </c>
+      <c r="F11" s="5">
+        <v>100</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D12" s="4">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4082</v>
+      </c>
+      <c r="F12" s="7">
+        <v>10</v>
+      </c>
+      <c r="G12" s="7">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" s="4">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2">
+        <v>14</v>
+      </c>
+      <c r="F13" s="5">
+        <v>20</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3947</v>
+      </c>
+      <c r="F14" s="7">
+        <v>30</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>150</v>
+      </c>
+      <c r="F15" s="5">
+        <v>40</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3574</v>
+      </c>
+      <c r="F16" s="7">
+        <v>50</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>523</v>
+      </c>
+      <c r="F17" s="5">
+        <v>60</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D18" s="4">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3743</v>
+      </c>
+      <c r="F18" s="7">
+        <v>70</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>353</v>
+      </c>
+      <c r="F19" s="5">
+        <v>80</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D20" s="4">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3687</v>
+      </c>
+      <c r="F20" s="7">
+        <v>90</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D21" s="4">
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>410</v>
+      </c>
+      <c r="F21" s="5">
+        <v>100</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D22" s="4">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2225</v>
+      </c>
+      <c r="F22" s="5">
+        <v>60</v>
+      </c>
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D23" s="4">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2">
+        <v>184</v>
+      </c>
+      <c r="F23" s="5">
+        <v>60</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D24" s="4">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4082</v>
+      </c>
+      <c r="F24" s="5">
+        <v>60</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" s="4">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2">
+        <v>14</v>
+      </c>
+      <c r="F25" s="5">
+        <v>60</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:9">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26" s="4">
+        <v>7</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <v>60</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:9">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>60</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:9">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>20</v>
+      </c>
+      <c r="F28" s="5">
+        <v>101</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:9">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>30</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>4097</v>
+      </c>
+      <c r="F30" s="7">
+        <v>10</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F31" s="5">
+        <v>20</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4097</v>
+      </c>
+      <c r="F32" s="7">
+        <v>30</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D33" s="4">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F33" s="5">
+        <v>40</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D34" s="4">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>4097</v>
+      </c>
+      <c r="F34" s="7">
+        <v>50</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F35" s="5">
+        <v>60</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D36" s="4">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2">
+        <v>4097</v>
+      </c>
+      <c r="F36" s="7">
+        <v>70</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F37" s="5">
+        <v>80</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D38" s="4">
+        <v>5</v>
+      </c>
+      <c r="E38" s="2">
+        <v>4097</v>
+      </c>
+      <c r="F38" s="7">
+        <v>90</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" s="4">
+        <v>5</v>
+      </c>
+      <c r="E39" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F39" s="5">
+        <v>100</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D40" s="4">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2">
+        <v>4097</v>
+      </c>
+      <c r="F40" s="7">
+        <v>10</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D41" s="4">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F41" s="5">
+        <v>20</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="5" width="22.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2048</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2048</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2048</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="27" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2048</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:6">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="19.1333333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10881,7 +12981,7 @@
       <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>33</v>
       </c>
       <c r="F2" t="s">
@@ -10889,7 +12989,7 @@
       </c>
     </row>
     <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -10901,11 +13001,2962 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
+    <col min="2" max="2" width="35.775" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18" style="4" customWidth="1"/>
+    <col min="4" max="4" width="39.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.775" style="6" customWidth="1"/>
+    <col min="7" max="8" width="14.775" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E2" s="7">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E3" s="5">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E4" s="7">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="5">
+        <v>40</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E6" s="7">
+        <v>50</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E7" s="5">
+        <v>60</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E8" s="7">
+        <v>70</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E9" s="5">
+        <v>80</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E10" s="7">
+        <v>90</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E11" s="5">
+        <v>100</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E12" s="7">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E13" s="5">
+        <v>20</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E14" s="7">
+        <v>30</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E15" s="5">
+        <v>40</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E16" s="7">
+        <v>50</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E17" s="5">
+        <v>60</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E18" s="7">
+        <v>70</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E19" s="5">
+        <v>80</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E20" s="7">
+        <v>90</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E21" s="5">
+        <v>100</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E22" s="5">
+        <v>60</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E23" s="5">
+        <v>60</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E24" s="5">
+        <v>60</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E25" s="5">
+        <v>60</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:8">
+      <c r="A26" s="4">
+        <v>27</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E26" s="5">
+        <v>101</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:8">
+      <c r="A27" s="2">
+        <v>28</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="4">
+        <v>29</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E28" s="7">
+        <v>10</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="4">
+        <v>30</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E29" s="5">
+        <v>20</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2">
+        <v>31</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E30" s="7">
+        <v>30</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="4">
+        <v>32</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E31" s="5">
+        <v>40</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E32" s="7">
+        <v>50</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="4">
+        <v>34</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E33" s="5">
+        <v>60</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="4">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E34" s="7">
+        <v>70</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E35" s="5">
+        <v>80</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="4">
+        <v>37</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E36" s="7">
+        <v>90</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="4">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E37" s="5">
+        <v>100</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2">
+        <v>39</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E38" s="7">
+        <v>10</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="4">
+        <v>40</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E39" s="5">
+        <v>20</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.5583333333333" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>168</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>135</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>150</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>145</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>160</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>180</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-168</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-135</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-150</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-145</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-155</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-180</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>155</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>110</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>150</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>155</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>155</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>160</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>155</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>110</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>169</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>136</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>151</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1">
+        <v>146</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1">
+        <v>161</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1">
+        <v>181</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-155</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-110</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-150</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-140</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-150</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-160</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-155</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-110</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-169</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-136</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-151</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-146</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-156</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-181</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.5583333333333" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="27" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D12" s="1">
+        <v>6</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:7">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -10920,11 +15971,11 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10959,11 +16010,636 @@
         <v>20</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="8" width="28.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>50</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>50</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="27" spans="1:9">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D4" s="1">
+        <v>254</v>
+      </c>
+      <c r="E4" s="1">
+        <v>50</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="27" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="27" spans="1:9">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>101</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="27" spans="1:9">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="27" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -10978,13 +16654,13 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
-    <col min="6" max="6" width="21.6333333333333" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.6333333333333" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.775" style="4" customWidth="1"/>
     <col min="8" max="8" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11004,10 +16680,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
@@ -11025,13 +16701,13 @@
         <v>24</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
         <v>1</v>
       </c>
       <c r="H2" t="s">
@@ -11039,7 +16715,7 @@
       </c>
     </row>
     <row r="3" ht="40.5" spans="1:8">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -11048,13 +16724,13 @@
       <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="E3" s="7">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" t="s">
@@ -11073,13 +16749,13 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
-    <col min="6" max="6" width="21.6333333333333" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.6333333333333" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.775" style="4" customWidth="1"/>
     <col min="8" max="8" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11099,10 +16775,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H1" t="s">
@@ -11120,13 +16796,13 @@
         <v>25</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>-1</v>
       </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
         <v>-1</v>
       </c>
       <c r="H2" t="s">
@@ -11134,7 +16810,7 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="40.5" spans="1:8">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -11143,13 +16819,13 @@
       <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="E3" s="7">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
         <v>-1</v>
       </c>
       <c r="H3" t="s">
@@ -11168,11 +16844,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11207,7 +16883,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">
@@ -11215,7 +16891,7 @@
       </c>
     </row>
     <row r="3" customFormat="1" ht="27" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -11224,7 +16900,7 @@
       <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="7">
         <v>0</v>
       </c>
       <c r="F3" t="s">
@@ -11243,11 +16919,11 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.225" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.225" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="20.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="14.775" customWidth="1"/>
-    <col min="5" max="5" width="14.775" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.775" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.775" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11282,7 +16958,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" t="s">

--- a/test_data/mycobot_280.xlsx
+++ b/test_data/mycobot_280.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14055" firstSheet="44" activeTab="51"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="42" activeTab="48"/>
   </bookViews>
   <sheets>
     <sheet name="get_modify_version" sheetId="4" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="481">
   <si>
     <t>ID</t>
   </si>
@@ -977,6 +977,9 @@
     <t>刷新模式下，使rz轴运动到正限位</t>
   </si>
   <si>
+    <t>设置坐标轴超限</t>
+  </si>
+  <si>
     <t>increment</t>
   </si>
   <si>
@@ -1133,9 +1136,6 @@
     <t>刷新模式下，使rz轴增量30mm运动</t>
   </si>
   <si>
-    <t>设置坐标轴超限</t>
-  </si>
-  <si>
     <t>设置x轴增量超限</t>
   </si>
   <si>
@@ -1449,9 +1449,6 @@
   </si>
   <si>
     <t>设置六关节刹车开关</t>
-  </si>
-  <si>
-    <t>设置开关状态超限</t>
   </si>
   <si>
     <t>使1关节掉电</t>
@@ -9511,7 +9508,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>299</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>274</v>
@@ -9535,7 +9532,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>85</v>
+        <v>299</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>274</v>
@@ -9638,7 +9635,7 @@
         <v>57</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>59</v>
@@ -9655,10 +9652,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -9681,10 +9678,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -9707,10 +9704,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -9733,10 +9730,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -9759,10 +9756,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -9785,10 +9782,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -9811,10 +9808,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -9837,10 +9834,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -9863,10 +9860,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -9889,10 +9886,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -9915,10 +9912,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -9941,10 +9938,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -9967,10 +9964,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -9993,10 +9990,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -10019,10 +10016,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -10045,10 +10042,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -10071,10 +10068,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -10097,10 +10094,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -10123,10 +10120,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -10149,10 +10146,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -10175,10 +10172,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -10201,10 +10198,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -10227,10 +10224,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -10253,10 +10250,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -10282,7 +10279,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -10306,7 +10303,7 @@
         <v>86</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -10330,7 +10327,7 @@
         <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -10354,7 +10351,7 @@
         <v>85</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -10375,10 +10372,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -10399,10 +10396,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -10454,7 +10451,7 @@
         <v>146</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>59</v>
@@ -10471,10 +10468,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -10497,10 +10494,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -10523,10 +10520,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -10549,10 +10546,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -10575,10 +10572,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -10601,10 +10598,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -10627,10 +10624,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -10653,10 +10650,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -10679,10 +10676,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -10705,10 +10702,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -10731,10 +10728,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -10757,10 +10754,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -10783,10 +10780,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -10809,10 +10806,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -10835,10 +10832,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -10861,10 +10858,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -10887,10 +10884,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -10913,10 +10910,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -10939,10 +10936,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -10965,10 +10962,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -10991,10 +10988,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -11017,10 +11014,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -11043,10 +11040,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -11069,10 +11066,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -11098,7 +11095,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -11122,7 +11119,7 @@
         <v>86</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -11143,10 +11140,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>351</v>
+        <v>299</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -11167,10 +11164,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>351</v>
+        <v>299</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -11194,7 +11191,7 @@
         <v>352</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -11218,7 +11215,7 @@
         <v>352</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -11877,7 +11874,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="2">
-        <v>2225</v>
+        <v>3808</v>
       </c>
       <c r="F10" s="7">
         <v>90</v>
@@ -11906,7 +11903,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="2">
-        <v>184</v>
+        <v>344</v>
       </c>
       <c r="F11" s="5">
         <v>100</v>
@@ -11935,7 +11932,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="2">
-        <v>4082</v>
+        <v>4028</v>
       </c>
       <c r="F12" s="7">
         <v>10</v>
@@ -11964,7 +11961,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F13" s="5">
         <v>20</v>
@@ -12225,7 +12222,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="2">
-        <v>2225</v>
+        <v>3808</v>
       </c>
       <c r="F22" s="5">
         <v>60</v>
@@ -12254,7 +12251,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="2">
-        <v>184</v>
+        <v>344</v>
       </c>
       <c r="F23" s="5">
         <v>60</v>
@@ -12283,7 +12280,7 @@
         <v>6</v>
       </c>
       <c r="E24" s="2">
-        <v>4082</v>
+        <v>4028</v>
       </c>
       <c r="F24" s="5">
         <v>60</v>
@@ -12312,7 +12309,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F25" s="5">
         <v>60</v>
@@ -14535,7 +14532,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -14558,7 +14555,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -14877,7 +14874,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>-150</v>
+        <v>-145</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -15568,19 +15565,19 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.225" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="28.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5583333333333" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15594,16 +15591,13 @@
         <v>57</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -15617,16 +15611,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -15642,14 +15633,11 @@
       <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -15663,16 +15651,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -15688,14 +15673,11 @@
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -15709,16 +15691,13 @@
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -15734,14 +15713,11 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -15755,16 +15731,13 @@
         <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -15780,14 +15753,11 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -15801,16 +15771,13 @@
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:6">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -15826,14 +15793,11 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:6">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -15847,16 +15811,13 @@
         <v>6</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:6">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -15872,14 +15833,11 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:6">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -15892,14 +15850,11 @@
       <c r="D14" s="1">
         <v>0</v>
       </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:7">
+    <row r="15" s="1" customFormat="1" spans="1:6">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -15912,50 +15867,7 @@
       <c r="D15" s="1">
         <v>7</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:7">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:7">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -16063,10 +15975,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16083,10 +15995,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16103,10 +16015,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16123,10 +16035,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -16143,10 +16055,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -16163,10 +16075,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -16186,7 +16098,7 @@
         <v>85</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -16203,7 +16115,7 @@
         <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -16258,10 +16170,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -16278,10 +16190,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -16298,10 +16210,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -16318,10 +16230,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -16338,10 +16250,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -16358,10 +16270,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -16381,7 +16293,7 @@
         <v>85</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -16398,7 +16310,7 @@
         <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -16439,16 +16351,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>4</v>
@@ -16462,10 +16374,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -16491,10 +16403,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -16514,10 +16426,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D4" s="1">
         <v>254</v>
@@ -16540,10 +16452,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -16567,10 +16479,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -16594,10 +16506,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -16621,10 +16533,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>

--- a/test_data/mycobot_280.xlsx
+++ b/test_data/mycobot_280.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="42" activeTab="48"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="37" activeTab="37"/>
   </bookViews>
   <sheets>
     <sheet name="get_modify_version" sheetId="4" r:id="rId1"/>
@@ -11671,7 +11671,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F3" s="5">
         <v>20</v>
@@ -11729,7 +11729,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="F5" s="5">
         <v>40</v>
@@ -11758,7 +11758,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="2">
-        <v>3743</v>
+        <v>3750</v>
       </c>
       <c r="F6" s="7">
         <v>50</v>
@@ -11787,7 +11787,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="F7" s="5">
         <v>60</v>
@@ -11816,7 +11816,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="2">
-        <v>3687</v>
+        <v>3705</v>
       </c>
       <c r="F8" s="7">
         <v>70</v>
@@ -11845,7 +11845,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="2">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="F9" s="5">
         <v>80</v>
@@ -11874,7 +11874,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="2">
-        <v>3808</v>
+        <v>3788</v>
       </c>
       <c r="F10" s="7">
         <v>90</v>
@@ -11932,7 +11932,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="2">
-        <v>4028</v>
+        <v>6</v>
       </c>
       <c r="F12" s="7">
         <v>10</v>
@@ -11961,7 +11961,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="2">
-        <v>68</v>
+        <v>4087</v>
       </c>
       <c r="F13" s="5">
         <v>20</v>
@@ -12019,7 +12019,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F15" s="5">
         <v>40</v>
@@ -12077,7 +12077,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="F17" s="5">
         <v>60</v>
@@ -12106,7 +12106,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="2">
-        <v>3743</v>
+        <v>3750</v>
       </c>
       <c r="F18" s="7">
         <v>70</v>
@@ -12135,7 +12135,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="F19" s="5">
         <v>80</v>
@@ -12164,7 +12164,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="2">
-        <v>3687</v>
+        <v>3705</v>
       </c>
       <c r="F20" s="7">
         <v>90</v>
@@ -12193,7 +12193,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="2">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="F21" s="5">
         <v>100</v>
@@ -12222,7 +12222,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="2">
-        <v>3808</v>
+        <v>3788</v>
       </c>
       <c r="F22" s="5">
         <v>60</v>
@@ -12280,7 +12280,7 @@
         <v>6</v>
       </c>
       <c r="E24" s="2">
-        <v>4028</v>
+        <v>6</v>
       </c>
       <c r="F24" s="5">
         <v>60</v>
@@ -12309,7 +12309,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="2">
-        <v>68</v>
+        <v>4087</v>
       </c>
       <c r="F25" s="5">
         <v>60</v>
